--- a/학교장추천_입결.xlsx
+++ b/학교장추천_입결.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE48FC8-7457-483F-BA34-EF843EC96B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8AC8E1-23BF-48B4-9B01-CD1393A8F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -517,97 +517,97 @@
   </si>
   <si>
     <t>4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>10</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>13</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>12</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>19</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>14</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>9</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>39</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>23</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>69</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>21</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>17</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>30</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>56</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,13 +726,6 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="major"/>
     </font>
     <font>
       <b/>
@@ -935,19 +928,13 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -959,8 +946,14 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1306,23 +1299,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="13" t="s">
@@ -1334,41 +1327,41 @@
       <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="29" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="30" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="31" t="s">
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="25" t="s">
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="26" t="s">
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="31" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1421,10 +1414,10 @@
       <c r="R3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="26"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
@@ -1539,13 +1532,13 @@
         <v>6</v>
       </c>
       <c r="P5" s="32">
-        <v>2.73</v>
+        <v>3.64</v>
       </c>
       <c r="Q5" s="32">
-        <v>2.64</v>
+        <v>3.03</v>
       </c>
       <c r="R5" s="32">
-        <v>2.4900000000000002</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="S5" s="24" t="s">
         <v>54</v>
@@ -1605,13 +1598,13 @@
         <v>7.8</v>
       </c>
       <c r="P6" s="32">
-        <v>3.64</v>
+        <v>2.73</v>
       </c>
       <c r="Q6" s="32">
-        <v>3.03</v>
+        <v>2.64</v>
       </c>
       <c r="R6" s="32">
-        <v>2.5299999999999998</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="S6" s="24" t="s">
         <v>56</v>
@@ -1671,13 +1664,13 @@
         <v>4</v>
       </c>
       <c r="P7" s="32">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="Q7" s="32">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="R7" s="32">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="S7" s="24" t="s">
         <v>59</v>
@@ -1737,13 +1730,13 @@
         <v>7.4</v>
       </c>
       <c r="P8" s="32">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" s="32">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="R8" s="32">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="S8" s="24" t="s">
         <v>55</v>
@@ -1869,13 +1862,13 @@
         <v>6.17</v>
       </c>
       <c r="P10" s="32">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" s="32">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R10" s="32">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="S10" s="24" t="s">
         <v>54</v>
@@ -1935,13 +1928,13 @@
         <v>3.5</v>
       </c>
       <c r="P11" s="32">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="Q11" s="32">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R11" s="32">
-        <v>3.15</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="S11" s="24" t="s">
         <v>55</v>
@@ -2001,13 +1994,13 @@
         <v>3.8</v>
       </c>
       <c r="P12" s="32">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="Q12" s="32">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="R12" s="32">
-        <v>2.5299999999999998</v>
+        <v>2.46</v>
       </c>
       <c r="S12" s="24" t="s">
         <v>55</v>
@@ -2067,13 +2060,13 @@
         <v>5.4</v>
       </c>
       <c r="P13" s="32">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" s="32">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R13" s="32">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="S13" s="24" t="s">
         <v>54</v>
@@ -2199,13 +2192,13 @@
         <v>5.75</v>
       </c>
       <c r="P15" s="32">
-        <v>3.29</v>
+        <v>3.81</v>
       </c>
       <c r="Q15" s="32">
-        <v>2.73</v>
+        <v>3.6</v>
       </c>
       <c r="R15" s="32">
-        <v>2.3199999999999998</v>
+        <v>3.4</v>
       </c>
       <c r="S15" s="24" t="s">
         <v>59</v>
@@ -2265,13 +2258,13 @@
         <v>11</v>
       </c>
       <c r="P16" s="32">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="Q16" s="32">
-        <v>3.24</v>
+        <v>2.73</v>
       </c>
       <c r="R16" s="32">
-        <v>2.84</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="S16" s="24" t="s">
         <v>59</v>
@@ -2599,13 +2592,13 @@
         <v>6.25</v>
       </c>
       <c r="P21" s="32">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="Q21" s="32">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="R21" s="32">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
       <c r="S21" s="24" t="s">
         <v>69</v>
@@ -2665,13 +2658,13 @@
         <v>7.75</v>
       </c>
       <c r="P22" s="32">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="Q22" s="32">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="R22" s="32">
-        <v>2.14</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="S22" s="24" t="s">
         <v>58</v>
@@ -2731,13 +2724,13 @@
         <v>7</v>
       </c>
       <c r="P23" s="32">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" s="32">
-        <v>3.01</v>
+        <v>3.11</v>
       </c>
       <c r="R23" s="32">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="S23" s="24" t="s">
         <v>59</v>
@@ -2797,13 +2790,13 @@
         <v>7.6</v>
       </c>
       <c r="P24" s="32">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q24" s="32">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="R24" s="32">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="S24" s="24" t="s">
         <v>56</v>
@@ -2863,13 +2856,13 @@
         <v>3.53</v>
       </c>
       <c r="P25" s="32">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" s="32">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="R25" s="32">
-        <v>2.93</v>
+        <v>2.14</v>
       </c>
       <c r="S25" s="24" t="s">
         <v>58</v>
@@ -2929,13 +2922,13 @@
         <v>3.53</v>
       </c>
       <c r="P26" s="32">
-        <v>3.83</v>
+        <v>4.34</v>
       </c>
       <c r="Q26" s="32">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="R26" s="32">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="S26" s="24" t="s">
         <v>54</v>
@@ -2995,13 +2988,13 @@
         <v>4.07</v>
       </c>
       <c r="P27" s="32">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="Q27" s="32">
-        <v>3.41</v>
+        <v>3.01</v>
       </c>
       <c r="R27" s="32">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="S27" s="24" t="s">
         <v>58</v>
@@ -3061,13 +3054,13 @@
         <v>5.93</v>
       </c>
       <c r="P28" s="32">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="32">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="R28" s="32">
-        <v>3.29</v>
+        <v>2.93</v>
       </c>
       <c r="S28" s="24" t="s">
         <v>55</v>
@@ -3127,13 +3120,13 @@
         <v>5.93</v>
       </c>
       <c r="P29" s="32">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="32">
-        <v>3.87</v>
+        <v>3.44</v>
       </c>
       <c r="R29" s="32">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
       <c r="S29" s="24" t="s">
         <v>56</v>
@@ -3193,13 +3186,13 @@
         <v>16.670000000000002</v>
       </c>
       <c r="P30" s="32">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="Q30" s="32">
-        <v>2.79</v>
+        <v>3.58</v>
       </c>
       <c r="R30" s="32">
-        <v>2.5099999999999998</v>
+        <v>3.11</v>
       </c>
       <c r="S30" s="24" t="s">
         <v>58</v>
@@ -3259,13 +3252,13 @@
         <v>6.1</v>
       </c>
       <c r="P31" s="32">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q31" s="32">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="R31" s="32">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="S31" s="24" t="s">
         <v>61</v>
@@ -3325,13 +3318,13 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="P32" s="32">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="Q32" s="32">
-        <v>3.11</v>
+        <v>3.39</v>
       </c>
       <c r="R32" s="32">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="S32" s="24" t="s">
         <v>54</v>
@@ -3391,13 +3384,13 @@
         <v>0</v>
       </c>
       <c r="P33" s="32">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="Q33" s="32">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="R33" s="32">
-        <v>2.97</v>
+        <v>2.34</v>
       </c>
       <c r="S33" s="24" t="s">
         <v>64</v>
@@ -3488,16 +3481,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/학교장추천_입결.xlsx
+++ b/학교장추천_입결.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8AC8E1-23BF-48B4-9B01-CD1393A8F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA7112-156F-490B-AD19-2A872E544639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>보건경영학과</t>
-  </si>
-  <si>
-    <t>스마트모빌리티공학과</t>
   </si>
   <si>
     <t>컴퓨터공학과</t>
@@ -601,6 +598,10 @@
   <si>
     <t>56</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트모빌리티공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -931,10 +932,19 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,15 +955,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1299,70 +1300,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="A1" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27" t="s">
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="28" t="s">
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="26" t="s">
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="30" t="s">
+      <c r="T2" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="U2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="27" t="s">
         <v>52</v>
-      </c>
-      <c r="V2" s="31" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="21.75">
@@ -1370,61 +1371,61 @@
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="N3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="R3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="30"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -1465,20 +1466,20 @@
       <c r="O4" s="8">
         <v>3.2</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="25">
         <v>2.5299999999999998</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="25">
         <v>2.34</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="25">
         <v>2.0499999999999998</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U4" s="24">
         <v>4</v>
@@ -1492,65 +1493,65 @@
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
-        <v>1</v>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="E5" s="3">
-        <v>2.88</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F5" s="2">
-        <v>2.3199999999999998</v>
+        <v>2.31</v>
       </c>
       <c r="G5" s="4">
-        <v>2.94</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="H5" s="5">
+        <v>3.86</v>
+      </c>
+      <c r="I5" s="4">
+        <v>3.43</v>
+      </c>
+      <c r="J5" s="6">
+        <v>2.98</v>
+      </c>
+      <c r="K5" s="7">
         <v>2.58</v>
       </c>
-      <c r="I5" s="4">
-        <v>2.02</v>
-      </c>
-      <c r="J5" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="K5" s="7">
-        <v>2.9</v>
-      </c>
       <c r="L5" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="M5" s="11">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M5" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N5" s="8">
         <v>4</v>
       </c>
-      <c r="N5" s="11">
-        <v>5.33</v>
-      </c>
-      <c r="O5" s="11">
-        <v>6</v>
-      </c>
-      <c r="P5" s="32">
-        <v>3.64</v>
-      </c>
-      <c r="Q5" s="32">
-        <v>3.03</v>
-      </c>
-      <c r="R5" s="32">
-        <v>2.5299999999999998</v>
+      <c r="O5" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="P5" s="25">
+        <v>2.73</v>
+      </c>
+      <c r="Q5" s="25">
+        <v>2.64</v>
+      </c>
+      <c r="R5" s="25">
+        <v>2.4900000000000002</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U5" s="24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V5" s="24">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1558,65 +1559,65 @@
         <v>3</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
+      <c r="C6" s="10" t="s">
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="E6" s="3">
-        <v>2.4300000000000002</v>
+        <v>2.88</v>
       </c>
       <c r="F6" s="2">
-        <v>2.31</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="G6" s="4">
-        <v>4.1100000000000003</v>
+        <v>2.94</v>
       </c>
       <c r="H6" s="5">
-        <v>3.86</v>
+        <v>2.58</v>
       </c>
       <c r="I6" s="4">
-        <v>3.43</v>
+        <v>2.02</v>
       </c>
       <c r="J6" s="6">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="K6" s="7">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="L6" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M6" s="8">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="N6" s="8">
+        <v>2.67</v>
+      </c>
+      <c r="M6" s="11">
         <v>4</v>
       </c>
-      <c r="O6" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="P6" s="32">
-        <v>2.73</v>
-      </c>
-      <c r="Q6" s="32">
-        <v>2.64</v>
-      </c>
-      <c r="R6" s="32">
-        <v>2.4900000000000002</v>
+      <c r="N6" s="11">
+        <v>5.33</v>
+      </c>
+      <c r="O6" s="11">
+        <v>6</v>
+      </c>
+      <c r="P6" s="25">
+        <v>3.64</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>3.03</v>
+      </c>
+      <c r="R6" s="25">
+        <v>2.5299999999999998</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="U6" s="24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V6" s="24">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1624,62 +1625,62 @@
         <v>4</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
-        <v>3</v>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="E7" s="3">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="F7" s="2">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G7" s="4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H7" s="5">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="I7" s="4">
-        <v>3.22</v>
+        <v>2.21</v>
       </c>
       <c r="J7" s="6">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="7">
-        <v>3.51</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="L7" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="M7" s="11">
-        <v>4.43</v>
-      </c>
-      <c r="N7" s="11">
-        <v>5.8</v>
-      </c>
-      <c r="O7" s="11">
+        <v>2.08</v>
+      </c>
+      <c r="M7" s="8">
+        <v>4.29</v>
+      </c>
+      <c r="N7" s="8">
         <v>4</v>
       </c>
-      <c r="P7" s="32">
-        <v>3.02</v>
-      </c>
-      <c r="Q7" s="32">
-        <v>2.9</v>
-      </c>
-      <c r="R7" s="32">
-        <v>2.74</v>
+      <c r="O7" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="P7" s="25">
+        <v>3.6</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>3.14</v>
+      </c>
+      <c r="R7" s="25">
+        <v>2.34</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="U7" s="24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V7" s="24">
         <v>12</v>
@@ -1690,62 +1691,62 @@
         <v>5</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2.82</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3.35</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="I8" s="4">
+        <v>3.22</v>
+      </c>
+      <c r="J8" s="6">
+        <v>3.86</v>
+      </c>
+      <c r="K8" s="7">
+        <v>3.51</v>
+      </c>
+      <c r="L8" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="M8" s="11">
+        <v>4.43</v>
+      </c>
+      <c r="N8" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="O8" s="11">
         <v>4</v>
       </c>
-      <c r="D8" s="2">
-        <v>3.38</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2.95</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G8" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="H8" s="5">
-        <v>2.77</v>
-      </c>
-      <c r="I8" s="4">
-        <v>2.21</v>
-      </c>
-      <c r="J8" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="K8" s="7">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="L8" s="6">
-        <v>2.08</v>
-      </c>
-      <c r="M8" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="N8" s="8">
-        <v>4</v>
-      </c>
-      <c r="O8" s="8">
-        <v>7.4</v>
-      </c>
-      <c r="P8" s="32">
-        <v>3.6</v>
-      </c>
-      <c r="Q8" s="32">
-        <v>3.14</v>
-      </c>
-      <c r="R8" s="32">
-        <v>2.34</v>
+      <c r="P8" s="25">
+        <v>3.02</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>2.9</v>
+      </c>
+      <c r="R8" s="25">
+        <v>2.74</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U8" s="24">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V8" s="24">
         <v>12</v>
@@ -1795,20 +1796,20 @@
       <c r="O9" s="11">
         <v>6.2</v>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="25">
         <v>3.22</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="25">
         <v>2.94</v>
       </c>
-      <c r="R9" s="32">
+      <c r="R9" s="25">
         <v>2.63</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U9" s="24">
         <v>13</v>
@@ -1823,64 +1824,64 @@
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2">
+        <v>3.26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2.27</v>
+      </c>
+      <c r="G10" s="4">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2.75</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2.56</v>
+      </c>
+      <c r="J10" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="K10" s="7">
         <v>3.23</v>
       </c>
-      <c r="E10" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2.86</v>
-      </c>
-      <c r="G10" s="4">
-        <v>4.25</v>
-      </c>
-      <c r="H10" s="5">
-        <v>3.55</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="J10" s="6">
-        <v>3.29</v>
-      </c>
-      <c r="K10" s="7">
-        <v>3.2</v>
-      </c>
       <c r="L10" s="6">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="M10" s="8">
-        <v>6.75</v>
+        <v>3.67</v>
       </c>
       <c r="N10" s="8">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="O10" s="8">
-        <v>6.17</v>
-      </c>
-      <c r="P10" s="32">
-        <v>3.4</v>
-      </c>
-      <c r="Q10" s="32">
-        <v>3.3</v>
-      </c>
-      <c r="R10" s="32">
-        <v>3.15</v>
+        <v>3.8</v>
+      </c>
+      <c r="P10" s="25">
+        <v>3.58</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>3</v>
+      </c>
+      <c r="R10" s="25">
+        <v>2.46</v>
       </c>
       <c r="S10" s="24" t="s">
         <v>54</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="U10" s="24">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V10" s="24">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1888,65 +1889,65 @@
         <v>8</v>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3.23</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.86</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4.25</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="J11" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="K11" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="L11" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="M11" s="8">
+        <v>6.75</v>
+      </c>
+      <c r="N11" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="O11" s="8">
+        <v>6.17</v>
+      </c>
+      <c r="P11" s="25">
+        <v>3.4</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>3.3</v>
+      </c>
+      <c r="R11" s="25">
+        <v>3.15</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="T11" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" s="24">
         <v>7</v>
       </c>
-      <c r="D11" s="2">
-        <v>3.57</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.15</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2.15</v>
-      </c>
-      <c r="G11" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="H11" s="5">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="I11" s="4">
-        <v>3.57</v>
-      </c>
-      <c r="J11" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="K11" s="7">
-        <v>3.53</v>
-      </c>
-      <c r="L11" s="6">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="M11" s="11">
-        <v>8.43</v>
-      </c>
-      <c r="N11" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="O11" s="11">
-        <v>3.5</v>
-      </c>
-      <c r="P11" s="32">
-        <v>3.77</v>
-      </c>
-      <c r="Q11" s="32">
-        <v>3.32</v>
-      </c>
-      <c r="R11" s="32">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="S11" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="U11" s="24">
-        <v>14</v>
-      </c>
       <c r="V11" s="24">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1954,65 +1955,65 @@
         <v>9</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
+      <c r="C12" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>3.26</v>
+        <v>3.57</v>
       </c>
       <c r="E12" s="3">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="F12" s="2">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="G12" s="4">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="H12" s="5">
-        <v>2.75</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I12" s="4">
-        <v>2.56</v>
+        <v>3.57</v>
       </c>
       <c r="J12" s="6">
-        <v>3.71</v>
+        <v>4.08</v>
       </c>
       <c r="K12" s="7">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="L12" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="M12" s="8">
-        <v>3.67</v>
-      </c>
-      <c r="N12" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="O12" s="8">
-        <v>3.8</v>
-      </c>
-      <c r="P12" s="32">
-        <v>3.58</v>
-      </c>
-      <c r="Q12" s="32">
-        <v>3</v>
-      </c>
-      <c r="R12" s="32">
-        <v>2.46</v>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="M12" s="11">
+        <v>8.43</v>
+      </c>
+      <c r="N12" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="O12" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="P12" s="25">
+        <v>3.77</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>3.32</v>
+      </c>
+      <c r="R12" s="25">
+        <v>2.5299999999999998</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="U12" s="24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V12" s="24">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2021,64 +2022,64 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="E13" s="3">
-        <v>3.08</v>
+        <v>3.52</v>
       </c>
       <c r="F13" s="2">
-        <v>2.58</v>
+        <v>3.22</v>
       </c>
       <c r="G13" s="4">
-        <v>3.71</v>
+        <v>4.04</v>
       </c>
       <c r="H13" s="5">
+        <v>3.56</v>
+      </c>
+      <c r="I13" s="4">
+        <v>3.18</v>
+      </c>
+      <c r="J13" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="K13" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="L13" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="M13" s="11">
+        <v>7</v>
+      </c>
+      <c r="N13" s="11">
+        <v>4</v>
+      </c>
+      <c r="O13" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="P13" s="25">
+        <v>3.81</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>3.6</v>
+      </c>
+      <c r="R13" s="25">
         <v>3.4</v>
       </c>
-      <c r="I13" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="J13" s="6">
-        <v>4.21</v>
-      </c>
-      <c r="K13" s="7">
-        <v>3.63</v>
-      </c>
-      <c r="L13" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="M13" s="11">
-        <v>6.83</v>
-      </c>
-      <c r="N13" s="11">
-        <v>13</v>
-      </c>
-      <c r="O13" s="11">
-        <v>5.4</v>
-      </c>
-      <c r="P13" s="32">
-        <v>3.55</v>
-      </c>
-      <c r="Q13" s="32">
-        <v>3.24</v>
-      </c>
-      <c r="R13" s="32">
-        <v>2.84</v>
-      </c>
       <c r="S13" s="24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U13" s="24">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="V13" s="24">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2125,20 +2126,20 @@
       <c r="O14" s="8">
         <v>6.4</v>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="25">
         <v>3.17</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="25">
         <v>2.91</v>
       </c>
-      <c r="R14" s="32">
+      <c r="R14" s="25">
         <v>2.59</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U14" s="24">
         <v>30</v>
@@ -2152,65 +2153,65 @@
         <v>12</v>
       </c>
       <c r="B15" s="9"/>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.96</v>
+      </c>
+      <c r="G15" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2.42</v>
+      </c>
+      <c r="I15" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J15" s="6">
+        <v>2.96</v>
+      </c>
+      <c r="K15" s="7">
+        <v>2.78</v>
+      </c>
+      <c r="L15" s="6">
+        <v>2.59</v>
+      </c>
+      <c r="M15" s="8">
+        <v>4.83</v>
+      </c>
+      <c r="N15" s="8">
+        <v>5.67</v>
+      </c>
+      <c r="O15" s="8">
         <v>11</v>
       </c>
-      <c r="D15" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3.52</v>
-      </c>
-      <c r="F15" s="2">
-        <v>3.22</v>
-      </c>
-      <c r="G15" s="4">
-        <v>4.04</v>
-      </c>
-      <c r="H15" s="5">
-        <v>3.56</v>
-      </c>
-      <c r="I15" s="4">
-        <v>3.18</v>
-      </c>
-      <c r="J15" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="K15" s="7">
-        <v>3.47</v>
-      </c>
-      <c r="L15" s="6">
-        <v>3.25</v>
-      </c>
-      <c r="M15" s="11">
-        <v>7</v>
-      </c>
-      <c r="N15" s="11">
-        <v>4</v>
-      </c>
-      <c r="O15" s="11">
-        <v>5.75</v>
-      </c>
-      <c r="P15" s="32">
-        <v>3.81</v>
-      </c>
-      <c r="Q15" s="32">
-        <v>3.6</v>
-      </c>
-      <c r="R15" s="32">
-        <v>3.4</v>
+      <c r="P15" s="25">
+        <v>3.29</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>2.73</v>
+      </c>
+      <c r="R15" s="25">
+        <v>2.3199999999999998</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="U15" s="24">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="V15" s="24">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2218,65 +2219,65 @@
         <v>13</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3.33</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.58</v>
+      </c>
+      <c r="G16" s="4">
+        <v>3.71</v>
+      </c>
+      <c r="H16" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="I16" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="J16" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="K16" s="7">
+        <v>3.63</v>
+      </c>
+      <c r="L16" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="M16" s="11">
+        <v>6.83</v>
+      </c>
+      <c r="N16" s="11">
+        <v>13</v>
+      </c>
+      <c r="O16" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="P16" s="25">
+        <v>3.55</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>3.24</v>
+      </c>
+      <c r="R16" s="25">
+        <v>2.84</v>
+      </c>
+      <c r="S16" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="T16" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="U16" s="24">
         <v>12</v>
       </c>
-      <c r="D16" s="2">
-        <v>2.93</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2.48</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1.96</v>
-      </c>
-      <c r="G16" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="H16" s="5">
-        <v>2.42</v>
-      </c>
-      <c r="I16" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J16" s="6">
-        <v>2.96</v>
-      </c>
-      <c r="K16" s="7">
-        <v>2.78</v>
-      </c>
-      <c r="L16" s="6">
-        <v>2.59</v>
-      </c>
-      <c r="M16" s="8">
-        <v>4.83</v>
-      </c>
-      <c r="N16" s="8">
-        <v>5.67</v>
-      </c>
-      <c r="O16" s="8">
-        <v>11</v>
-      </c>
-      <c r="P16" s="32">
-        <v>3.29</v>
-      </c>
-      <c r="Q16" s="32">
-        <v>2.73</v>
-      </c>
-      <c r="R16" s="32">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="S16" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="T16" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="U16" s="24">
-        <v>18</v>
-      </c>
       <c r="V16" s="24">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2323,20 +2324,20 @@
       <c r="O17" s="11">
         <v>3.8</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="25">
         <v>2.91</v>
       </c>
-      <c r="Q17" s="32">
+      <c r="Q17" s="25">
         <v>2.59</v>
       </c>
-      <c r="R17" s="32">
+      <c r="R17" s="25">
         <v>1.96</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U17" s="24">
         <v>12</v>
@@ -2350,7 +2351,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
@@ -2391,20 +2392,20 @@
       <c r="O18" s="8">
         <v>10.130000000000001</v>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="25">
         <v>3.54</v>
       </c>
-      <c r="Q18" s="32">
+      <c r="Q18" s="25">
         <v>3.07</v>
       </c>
-      <c r="R18" s="32">
+      <c r="R18" s="25">
         <v>2.36</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U18" s="24">
         <v>16</v>
@@ -2457,20 +2458,20 @@
       <c r="O19" s="11">
         <v>5.4</v>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="25">
         <v>3.01</v>
       </c>
-      <c r="Q19" s="32">
+      <c r="Q19" s="25">
         <v>2.73</v>
       </c>
-      <c r="R19" s="32">
+      <c r="R19" s="25">
         <v>2.2799999999999998</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U19" s="24">
         <v>8</v>
@@ -2523,20 +2524,20 @@
       <c r="O20" s="8">
         <v>12.2</v>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="25">
         <v>3.01</v>
       </c>
-      <c r="Q20" s="32">
+      <c r="Q20" s="25">
         <v>2.85</v>
       </c>
-      <c r="R20" s="32">
+      <c r="R20" s="25">
         <v>2.73</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U20" s="24">
         <v>11</v>
@@ -2550,67 +2551,67 @@
         <v>18</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="E21" s="3">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="F21" s="2">
-        <v>2.78</v>
+        <v>2.27</v>
       </c>
       <c r="G21" s="4">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="H21" s="5">
-        <v>3.54</v>
+        <v>3.99</v>
       </c>
       <c r="I21" s="4">
-        <v>2.96</v>
+        <v>2.29</v>
       </c>
       <c r="J21" s="6">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="K21" s="7">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="L21" s="6">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M21" s="11">
-        <v>3.67</v>
+        <v>6.58</v>
       </c>
       <c r="N21" s="11">
-        <v>6.58</v>
+        <v>2.9</v>
       </c>
       <c r="O21" s="11">
-        <v>6.25</v>
-      </c>
-      <c r="P21" s="32">
-        <v>4.04</v>
-      </c>
-      <c r="Q21" s="32">
-        <v>3.55</v>
-      </c>
-      <c r="R21" s="32">
-        <v>2.97</v>
+        <v>0</v>
+      </c>
+      <c r="P21" s="25">
+        <v>3.76</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>3.33</v>
+      </c>
+      <c r="R21" s="25">
+        <v>2.34</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="T21" s="24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U21" s="24">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="V21" s="24">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2618,65 +2619,65 @@
         <v>19</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
+      <c r="C22" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="2">
+        <v>3.15</v>
+      </c>
+      <c r="E22" s="3">
         <v>2.72</v>
       </c>
-      <c r="E22" s="3">
-        <v>2.58</v>
-      </c>
       <c r="F22" s="2">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="G22" s="4">
-        <v>2.83</v>
+        <v>3.51</v>
       </c>
       <c r="H22" s="5">
-        <v>2.66</v>
+        <v>3.31</v>
       </c>
       <c r="I22" s="4">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="J22" s="6">
-        <v>2.99</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="K22" s="7">
-        <v>2.5499999999999998</v>
+        <v>3.64</v>
       </c>
       <c r="L22" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="M22" s="8">
-        <v>3.86</v>
-      </c>
-      <c r="N22" s="8">
-        <v>3.57</v>
-      </c>
-      <c r="O22" s="8">
-        <v>7.75</v>
-      </c>
-      <c r="P22" s="32">
-        <v>2.99</v>
-      </c>
-      <c r="Q22" s="32">
-        <v>2.79</v>
-      </c>
-      <c r="R22" s="32">
-        <v>2.5099999999999998</v>
+        <v>1.49</v>
+      </c>
+      <c r="M22" s="11">
+        <v>5</v>
+      </c>
+      <c r="N22" s="11">
+        <v>7.25</v>
+      </c>
+      <c r="O22" s="11">
+        <v>3.53</v>
+      </c>
+      <c r="P22" s="25">
+        <v>3.28</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>2.89</v>
+      </c>
+      <c r="R22" s="25">
+        <v>2.14</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="U22" s="24">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="V22" s="24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2684,65 +2685,65 @@
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
-      <c r="C23" s="9" t="s">
-        <v>19</v>
+      <c r="C23" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="2">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="E23" s="3">
-        <v>3.07</v>
+        <v>2.79</v>
       </c>
       <c r="F23" s="2">
-        <v>2.86</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G23" s="4">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="H23" s="5">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="I23" s="4">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="J23" s="6">
-        <v>3.14</v>
+        <v>3.37</v>
       </c>
       <c r="K23" s="7">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="L23" s="6">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="M23" s="11">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N23" s="11">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="O23" s="11">
-        <v>7</v>
-      </c>
-      <c r="P23" s="32">
-        <v>3.36</v>
-      </c>
-      <c r="Q23" s="32">
-        <v>3.11</v>
-      </c>
-      <c r="R23" s="32">
-        <v>2.67</v>
+        <v>4.07</v>
+      </c>
+      <c r="P23" s="25">
+        <v>3.34</v>
+      </c>
+      <c r="Q23" s="25">
+        <v>3.01</v>
+      </c>
+      <c r="R23" s="25">
+        <v>2.46</v>
       </c>
       <c r="S23" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T23" s="24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="U23" s="24">
         <v>7</v>
       </c>
-      <c r="V23" s="24">
-        <v>6</v>
+      <c r="V23" s="24" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2750,65 +2751,65 @@
         <v>21</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="1" t="s">
-        <v>20</v>
+      <c r="C24" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="D24" s="2">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="E24" s="3">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="G24" s="4">
-        <v>4.99</v>
+        <v>3.97</v>
       </c>
       <c r="H24" s="5">
-        <v>4.1900000000000004</v>
+        <v>3.59</v>
       </c>
       <c r="I24" s="4">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="J24" s="6">
-        <v>3.29</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="K24" s="7">
-        <v>3</v>
+        <v>3.71</v>
       </c>
       <c r="L24" s="6">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="M24" s="8">
-        <v>7.38</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N24" s="8">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O24" s="8">
-        <v>7.6</v>
-      </c>
-      <c r="P24" s="32">
-        <v>3.75</v>
-      </c>
-      <c r="Q24" s="32">
-        <v>3.53</v>
-      </c>
-      <c r="R24" s="32">
-        <v>3.22</v>
+        <v>5.93</v>
+      </c>
+      <c r="P24" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>3.44</v>
+      </c>
+      <c r="R24" s="25">
+        <v>2.93</v>
       </c>
       <c r="S24" s="24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T24" s="24" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="U24" s="24">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="V24" s="24">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2817,64 +2818,64 @@
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D25" s="2">
-        <v>3.15</v>
+        <v>3.81</v>
       </c>
       <c r="E25" s="3">
-        <v>2.72</v>
+        <v>3.28</v>
       </c>
       <c r="F25" s="2">
-        <v>1.97</v>
+        <v>2.73</v>
       </c>
       <c r="G25" s="4">
-        <v>3.51</v>
+        <v>3.97</v>
       </c>
       <c r="H25" s="5">
-        <v>3.31</v>
+        <v>3.59</v>
       </c>
       <c r="I25" s="4">
         <v>3.04</v>
       </c>
       <c r="J25" s="6">
-        <v>4.2300000000000004</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="K25" s="7">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="L25" s="6">
-        <v>1.49</v>
+        <v>2.92</v>
       </c>
       <c r="M25" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N25" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="O25" s="11">
+        <v>5.93</v>
+      </c>
+      <c r="P25" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="25">
+        <v>3.44</v>
+      </c>
+      <c r="R25" s="25">
+        <v>2.93</v>
+      </c>
+      <c r="S25" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="T25" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="U25" s="24">
+        <v>13</v>
+      </c>
+      <c r="V25" s="24">
         <v>5</v>
-      </c>
-      <c r="N25" s="11">
-        <v>7.25</v>
-      </c>
-      <c r="O25" s="11">
-        <v>3.53</v>
-      </c>
-      <c r="P25" s="32">
-        <v>3.28</v>
-      </c>
-      <c r="Q25" s="32">
-        <v>2.89</v>
-      </c>
-      <c r="R25" s="32">
-        <v>2.14</v>
-      </c>
-      <c r="S25" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="T25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="U25" s="24">
-        <v>23</v>
-      </c>
-      <c r="V25" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2883,64 +2884,64 @@
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2">
-        <v>4.3</v>
+        <v>3.96</v>
       </c>
       <c r="E26" s="3">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="F26" s="2">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
       <c r="G26" s="4">
-        <v>3.51</v>
+        <v>5.29</v>
       </c>
       <c r="H26" s="5">
-        <v>3.31</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="I26" s="4">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="J26" s="6">
-        <v>4.2300000000000004</v>
+        <v>3.73</v>
       </c>
       <c r="K26" s="7">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="L26" s="6">
-        <v>1.49</v>
+        <v>3.37</v>
       </c>
       <c r="M26" s="8">
-        <v>3.33</v>
+        <v>14.8</v>
       </c>
       <c r="N26" s="8">
-        <v>7.25</v>
+        <v>3.2</v>
       </c>
       <c r="O26" s="8">
-        <v>3.53</v>
-      </c>
-      <c r="P26" s="32">
-        <v>4.34</v>
-      </c>
-      <c r="Q26" s="32">
-        <v>3.87</v>
-      </c>
-      <c r="R26" s="32">
-        <v>3.19</v>
+        <v>16.670000000000002</v>
+      </c>
+      <c r="P26" s="25">
+        <v>3.83</v>
+      </c>
+      <c r="Q26" s="25">
+        <v>3.58</v>
+      </c>
+      <c r="R26" s="25">
+        <v>3.11</v>
       </c>
       <c r="S26" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="T26" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="T26" s="24" t="s">
-        <v>58</v>
-      </c>
       <c r="U26" s="24">
+        <v>6</v>
+      </c>
+      <c r="V26" s="24">
         <v>8</v>
-      </c>
-      <c r="V26" s="24">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2949,64 +2950,64 @@
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="E27" s="3">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="F27" s="2">
-        <v>2.2599999999999998</v>
+        <v>3.14</v>
       </c>
       <c r="G27" s="4">
-        <v>3.53</v>
+        <v>4.55</v>
       </c>
       <c r="H27" s="5">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="I27" s="4">
-        <v>2.23</v>
+        <v>2.76</v>
       </c>
       <c r="J27" s="6">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="K27" s="7">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="L27" s="6">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="M27" s="11">
-        <v>6.5</v>
+        <v>3.83</v>
       </c>
       <c r="N27" s="11">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="O27" s="11">
-        <v>4.07</v>
-      </c>
-      <c r="P27" s="32">
-        <v>3.34</v>
-      </c>
-      <c r="Q27" s="32">
-        <v>3.01</v>
-      </c>
-      <c r="R27" s="32">
-        <v>2.46</v>
+        <v>6.1</v>
+      </c>
+      <c r="P27" s="25">
+        <v>3.54</v>
+      </c>
+      <c r="Q27" s="25">
+        <v>3.41</v>
+      </c>
+      <c r="R27" s="25">
+        <v>3.08</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="U27" s="24">
-        <v>7</v>
-      </c>
-      <c r="V27" s="24" t="s">
-        <v>72</v>
+        <v>12</v>
+      </c>
+      <c r="V27" s="24">
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3015,64 +3016,64 @@
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D28" s="2">
-        <v>3.81</v>
+        <v>3.27</v>
       </c>
       <c r="E28" s="3">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="F28" s="2">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="G28" s="4">
-        <v>3.97</v>
+        <v>3.46</v>
       </c>
       <c r="H28" s="5">
-        <v>3.59</v>
+        <v>3.13</v>
       </c>
       <c r="I28" s="4">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="J28" s="6">
-        <v>4.2699999999999996</v>
+        <v>3.47</v>
       </c>
       <c r="K28" s="7">
-        <v>3.71</v>
+        <v>3.26</v>
       </c>
       <c r="L28" s="6">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="M28" s="8">
-        <v>4.5999999999999996</v>
+        <v>5.67</v>
       </c>
       <c r="N28" s="8">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="O28" s="8">
-        <v>5.93</v>
-      </c>
-      <c r="P28" s="32">
-        <v>4</v>
-      </c>
-      <c r="Q28" s="32">
-        <v>3.44</v>
-      </c>
-      <c r="R28" s="32">
-        <v>2.93</v>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P28" s="25">
+        <v>3.47</v>
+      </c>
+      <c r="Q28" s="25">
+        <v>3.39</v>
+      </c>
+      <c r="R28" s="25">
+        <v>3.29</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U28" s="24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V28" s="24">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3080,62 +3081,62 @@
         <v>26</v>
       </c>
       <c r="B29" s="9"/>
-      <c r="C29" s="10" t="s">
-        <v>24</v>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D29" s="2">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
       <c r="E29" s="3">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="F29" s="2">
-        <v>2.73</v>
+        <v>3.13</v>
       </c>
       <c r="G29" s="4">
-        <v>3.97</v>
+        <v>3.51</v>
       </c>
       <c r="H29" s="5">
-        <v>3.59</v>
+        <v>3.31</v>
       </c>
       <c r="I29" s="4">
         <v>3.04</v>
       </c>
       <c r="J29" s="6">
-        <v>4.2699999999999996</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="K29" s="7">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="L29" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="M29" s="11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N29" s="11">
-        <v>4.8</v>
-      </c>
-      <c r="O29" s="11">
-        <v>5.93</v>
-      </c>
-      <c r="P29" s="32">
-        <v>4</v>
-      </c>
-      <c r="Q29" s="32">
-        <v>3.44</v>
-      </c>
-      <c r="R29" s="32">
-        <v>2.93</v>
+        <v>1.49</v>
+      </c>
+      <c r="M29" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="N29" s="8">
+        <v>7.25</v>
+      </c>
+      <c r="O29" s="8">
+        <v>3.53</v>
+      </c>
+      <c r="P29" s="25">
+        <v>4.34</v>
+      </c>
+      <c r="Q29" s="25">
+        <v>3.87</v>
+      </c>
+      <c r="R29" s="25">
+        <v>3.19</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="U29" s="24">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V29" s="24">
         <v>5</v>
@@ -3147,64 +3148,64 @@
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2">
-        <v>3.96</v>
+        <v>2.72</v>
       </c>
       <c r="E30" s="3">
-        <v>3.54</v>
+        <v>2.58</v>
       </c>
       <c r="F30" s="2">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="G30" s="4">
-        <v>5.29</v>
+        <v>2.83</v>
       </c>
       <c r="H30" s="5">
-        <v>4.3899999999999997</v>
+        <v>2.66</v>
       </c>
       <c r="I30" s="4">
-        <v>3.27</v>
+        <v>2.4</v>
       </c>
       <c r="J30" s="6">
-        <v>3.73</v>
+        <v>2.99</v>
       </c>
       <c r="K30" s="7">
-        <v>3.58</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="L30" s="6">
-        <v>3.37</v>
+        <v>1.45</v>
       </c>
       <c r="M30" s="8">
-        <v>14.8</v>
+        <v>3.86</v>
       </c>
       <c r="N30" s="8">
-        <v>3.2</v>
+        <v>3.57</v>
       </c>
       <c r="O30" s="8">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="P30" s="32">
-        <v>3.83</v>
-      </c>
-      <c r="Q30" s="32">
-        <v>3.58</v>
-      </c>
-      <c r="R30" s="32">
-        <v>3.11</v>
+        <v>7.75</v>
+      </c>
+      <c r="P30" s="25">
+        <v>2.99</v>
+      </c>
+      <c r="Q30" s="25">
+        <v>2.79</v>
+      </c>
+      <c r="R30" s="25">
+        <v>2.5099999999999998</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U30" s="24">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="V30" s="24">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3212,65 +3213,65 @@
         <v>28</v>
       </c>
       <c r="B31" s="9"/>
-      <c r="C31" s="10" t="s">
-        <v>27</v>
+      <c r="C31" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D31" s="2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E31" s="3">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="F31" s="2">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="G31" s="4">
-        <v>4.55</v>
+        <v>4.99</v>
       </c>
       <c r="H31" s="5">
-        <v>3.6</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I31" s="4">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="J31" s="6">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="K31" s="7">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="L31" s="6">
-        <v>2.56</v>
-      </c>
-      <c r="M31" s="11">
-        <v>3.83</v>
-      </c>
-      <c r="N31" s="11">
-        <v>2.4</v>
-      </c>
-      <c r="O31" s="11">
-        <v>6.1</v>
-      </c>
-      <c r="P31" s="32">
-        <v>3.54</v>
-      </c>
-      <c r="Q31" s="32">
-        <v>3.41</v>
-      </c>
-      <c r="R31" s="32">
-        <v>3.08</v>
+        <v>2.46</v>
+      </c>
+      <c r="M31" s="8">
+        <v>7.38</v>
+      </c>
+      <c r="N31" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="O31" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="P31" s="25">
+        <v>3.75</v>
+      </c>
+      <c r="Q31" s="25">
+        <v>3.53</v>
+      </c>
+      <c r="R31" s="25">
+        <v>3.22</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="U31" s="24">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V31" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3278,65 +3279,65 @@
         <v>29</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="12" t="s">
-        <v>28</v>
+      <c r="C32" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="D32" s="2">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="E32" s="3">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="F32" s="2">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="G32" s="4">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="H32" s="5">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="I32" s="4">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="6">
-        <v>3.47</v>
+        <v>3.14</v>
       </c>
       <c r="K32" s="7">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="L32" s="6">
-        <v>2.72</v>
-      </c>
-      <c r="M32" s="8">
-        <v>5.67</v>
-      </c>
-      <c r="N32" s="8">
-        <v>3.75</v>
-      </c>
-      <c r="O32" s="8">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="P32" s="32">
-        <v>3.47</v>
-      </c>
-      <c r="Q32" s="32">
-        <v>3.39</v>
-      </c>
-      <c r="R32" s="32">
-        <v>3.29</v>
+        <v>2.57</v>
+      </c>
+      <c r="M32" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="N32" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="O32" s="11">
+        <v>7</v>
+      </c>
+      <c r="P32" s="25">
+        <v>3.36</v>
+      </c>
+      <c r="Q32" s="25">
+        <v>3.11</v>
+      </c>
+      <c r="R32" s="25">
+        <v>2.67</v>
       </c>
       <c r="S32" s="24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T32" s="24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="U32" s="24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V32" s="24">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3345,64 +3346,64 @@
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="10" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="D33" s="2">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="E33" s="3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="F33" s="2">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="G33" s="4">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="H33" s="5">
-        <v>3.99</v>
+        <v>3.54</v>
       </c>
       <c r="I33" s="4">
-        <v>2.29</v>
+        <v>2.96</v>
       </c>
       <c r="J33" s="6">
+        <v>4.29</v>
+      </c>
+      <c r="K33" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="L33" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="M33" s="11">
+        <v>3.67</v>
+      </c>
+      <c r="N33" s="11">
+        <v>6.58</v>
+      </c>
+      <c r="O33" s="11">
+        <v>6.25</v>
+      </c>
+      <c r="P33" s="25">
+        <v>4.04</v>
+      </c>
+      <c r="Q33" s="25">
+        <v>3.55</v>
+      </c>
+      <c r="R33" s="25">
+        <v>2.97</v>
+      </c>
+      <c r="S33" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="T33" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="U33" s="24">
+        <v>61</v>
+      </c>
+      <c r="V33" s="24">
         <v>0</v>
-      </c>
-      <c r="K33" s="7">
-        <v>0</v>
-      </c>
-      <c r="L33" s="6">
-        <v>0</v>
-      </c>
-      <c r="M33" s="11">
-        <v>6.58</v>
-      </c>
-      <c r="N33" s="11">
-        <v>2.9</v>
-      </c>
-      <c r="O33" s="11">
-        <v>0</v>
-      </c>
-      <c r="P33" s="32">
-        <v>3.76</v>
-      </c>
-      <c r="Q33" s="32">
-        <v>3.33</v>
-      </c>
-      <c r="R33" s="32">
-        <v>2.34</v>
-      </c>
-      <c r="S33" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="T33" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="U33" s="24">
-        <v>32</v>
-      </c>
-      <c r="V33" s="24">
-        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3410,10 +3411,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2">
         <v>3.18</v>
@@ -3451,20 +3452,20 @@
       <c r="O34" s="8">
         <v>0</v>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="25">
         <v>3.45</v>
       </c>
-      <c r="Q34" s="32">
+      <c r="Q34" s="25">
         <v>3.15</v>
       </c>
-      <c r="R34" s="32">
+      <c r="R34" s="25">
         <v>2.73</v>
       </c>
       <c r="S34" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="T34" s="24" t="s">
         <v>74</v>
-      </c>
-      <c r="T34" s="24" t="s">
-        <v>75</v>
       </c>
       <c r="U34" s="24">
         <v>25</v>
@@ -3481,16 +3482,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/학교장추천_입결.xlsx
+++ b/학교장추천_입결.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA7112-156F-490B-AD19-2A872E544639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC88720-567A-4D7A-BF79-F25B2134C7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
@@ -935,16 +935,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -955,6 +949,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1300,23 +1300,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="13" t="s">
@@ -1328,41 +1328,41 @@
       <c r="C2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="30" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="32" t="s">
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="28" t="s">
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="26" t="s">
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="32" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1415,10 +1415,10 @@
       <c r="R3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="26"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
@@ -1542,16 +1542,16 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="U5" s="24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V5" s="24">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1608,16 +1608,16 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="U6" s="24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V6" s="24">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1674,13 +1674,13 @@
         <v>2.34</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="U7" s="24">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V7" s="24">
         <v>12</v>
@@ -1740,13 +1740,13 @@
         <v>2.74</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="U8" s="24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V8" s="24">
         <v>12</v>
@@ -1872,16 +1872,16 @@
         <v>2.46</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U10" s="24">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V10" s="24">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1938,16 +1938,16 @@
         <v>3.15</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="U11" s="24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V11" s="24">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2007,13 +2007,13 @@
         <v>54</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="U12" s="24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V12" s="24">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2070,16 +2070,16 @@
         <v>3.4</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U13" s="24">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="V13" s="24">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2205,13 +2205,13 @@
         <v>58</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U15" s="24">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="V15" s="24">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2268,16 +2268,16 @@
         <v>2.84</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="U16" s="24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V16" s="24">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2602,16 +2602,16 @@
         <v>2.34</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="T21" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U21" s="24">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="V21" s="24">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2671,13 +2671,13 @@
         <v>57</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="U22" s="24">
-        <v>23</v>
-      </c>
-      <c r="V22" s="24">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="V22" s="24" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2734,16 +2734,16 @@
         <v>2.46</v>
       </c>
       <c r="S23" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T23" s="24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U23" s="24">
         <v>7</v>
       </c>
-      <c r="V23" s="24" t="s">
-        <v>71</v>
+      <c r="V23" s="24">
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2800,16 +2800,16 @@
         <v>2.93</v>
       </c>
       <c r="S24" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T24" s="24" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="U24" s="24">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="V24" s="24">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2866,16 +2866,16 @@
         <v>2.93</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="U25" s="24">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="V25" s="24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2932,16 +2932,16 @@
         <v>3.11</v>
       </c>
       <c r="S26" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="T26" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="T26" s="24" t="s">
-        <v>54</v>
-      </c>
       <c r="U26" s="24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V26" s="24">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2998,16 +2998,16 @@
         <v>3.08</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="U27" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V27" s="24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3064,16 +3064,16 @@
         <v>3.29</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="U28" s="24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V28" s="24">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3130,13 +3130,13 @@
         <v>3.19</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U29" s="24">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V29" s="24">
         <v>5</v>
@@ -3199,13 +3199,13 @@
         <v>57</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U30" s="24">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V30" s="24">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3262,16 +3262,16 @@
         <v>3.22</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U31" s="24">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V31" s="24">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3328,16 +3328,16 @@
         <v>2.67</v>
       </c>
       <c r="S32" s="24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="T32" s="24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U32" s="24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V32" s="24">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3394,16 +3394,16 @@
         <v>2.97</v>
       </c>
       <c r="S33" s="24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="T33" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U33" s="24">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="V33" s="24">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3482,16 +3482,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
